--- a/JsonConverter/ExcelFiles/Weapon.xlsx
+++ b/JsonConverter/ExcelFiles/Weapon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\Project\Vamsurlike\Vamsurlike\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8ACB77-7C2A-490A-9AD5-B50C05B89748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC535F4-1088-41D2-9616-D7B61A577D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="816" windowWidth="28284" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WeaponStats" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="140">
   <si>
     <t>108Bocce</t>
   </si>
@@ -77,9 +77,6 @@
   </si>
   <si>
     <t>0.05</t>
-  </si>
-  <si>
-    <t>Axe</t>
   </si>
   <si>
     <t>70</t>
@@ -1844,8 +1841,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="WeaponStatsTable" displayName="WeaponStatsTable" ref="A3:P37" headerRowDxfId="21" dataDxfId="20" totalsRowDxfId="19">
-  <autoFilter ref="A3:P37" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="WeaponStatsTable" displayName="WeaponStatsTable" ref="A3:P36" headerRowDxfId="21" dataDxfId="20" totalsRowDxfId="19">
+  <autoFilter ref="A3:P36" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="16">
     <tableColumn id="13" xr3:uid="{860DCEDD-19C2-4C46-B1C4-67945C167C76}" name="Id" dataDxfId="18" dataCellStyle="Normal"/>
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Name" dataDxfId="17"/>
@@ -2017,7 +2014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P37"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="11.5" style="2" customWidth="1"/>
@@ -2033,124 +2030,124 @@
       <c r="A1" s="1"/>
       <c r="C1" s="2"/>
       <c r="D1" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E1" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>85</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>86</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="G2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="L2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="N2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>68</v>
-      </c>
       <c r="O2" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="17.55" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="I3" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="F3" s="9" t="s">
+      <c r="J3" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="G3" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="I3" s="9" t="s">
+      <c r="M3" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="N3" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="O3" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="J3" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="N3" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="O3" s="12" t="s">
-        <v>95</v>
-      </c>
       <c r="P3" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2174,7 +2171,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I4" s="7"/>
       <c r="J4" s="7">
@@ -2189,7 +2186,7 @@
       <c r="M4" s="7"/>
       <c r="N4" s="10"/>
       <c r="O4" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P4" s="10"/>
     </row>
@@ -2198,7 +2195,7 @@
         <v>263003</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C5" s="5">
         <v>8</v>
@@ -2236,21 +2233,21 @@
         <v>5</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="4">
-        <v>263010</v>
+        <v>263020</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C6" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E6" s="7">
         <v>1</v>
@@ -2259,16 +2256,16 @@
         <v>2</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="J6" s="7">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>2</v>
@@ -2278,154 +2275,154 @@
       </c>
       <c r="M6" s="7"/>
       <c r="N6" s="18">
-        <v>264004</v>
-      </c>
-      <c r="O6" s="10" t="s">
-        <v>97</v>
+        <v>264027</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="4">
-        <v>263020</v>
+        <v>263023</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="5">
-        <v>7</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="7">
-        <v>1</v>
-      </c>
-      <c r="F7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="7">
         <v>2</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J7" s="7">
-        <v>10</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="7"/>
       <c r="N7" s="18">
-        <v>264027</v>
+        <v>264016</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>27</v>
+        <v>117</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="4">
-        <v>263023</v>
+        <v>263036</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" s="5">
         <v>8</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
+      <c r="D8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="7">
+        <v>4</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="G8" s="7" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
+      <c r="I8" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="7">
+        <v>10</v>
+      </c>
+      <c r="K8" s="8">
+        <v>1</v>
+      </c>
       <c r="L8" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="M8" s="7">
-        <v>2</v>
-      </c>
-      <c r="N8" s="18">
-        <v>264016</v>
+        <v>14</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>118</v>
+        <v>30</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" ht="17.399999999999999">
       <c r="A9" s="4">
-        <v>263036</v>
+        <v>263037</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C9" s="5">
         <v>8</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E9" s="7">
-        <v>4</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>33</v>
+        <v>1</v>
+      </c>
+      <c r="F9" s="8">
+        <v>1</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="J9" s="7">
-        <v>10</v>
-      </c>
-      <c r="K9" s="8">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>2</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>21</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="M9" s="7"/>
       <c r="O9" s="6" t="s">
-        <v>31</v>
+        <v>111</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="17.399999999999999">
+    <row r="10" spans="1:16">
       <c r="A10" s="4">
-        <v>263037</v>
+        <v>263041</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>34</v>
       </c>
       <c r="C10" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>6</v>
@@ -2433,60 +2430,60 @@
       <c r="E10" s="7">
         <v>1</v>
       </c>
-      <c r="F10" s="8">
-        <v>1</v>
-      </c>
+      <c r="F10" s="7"/>
       <c r="G10" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>13</v>
       </c>
       <c r="J10" s="7">
-        <v>5</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="K10" s="8">
+        <v>1</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="M10" s="7"/>
       <c r="O10" s="6" t="s">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="4">
-        <v>263041</v>
+        <v>263046</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C11" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="7">
-        <v>1</v>
-      </c>
-      <c r="F11" s="7"/>
+      <c r="E11" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="8">
+        <v>1</v>
+      </c>
       <c r="G11" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="7" t="s">
         <v>36</v>
       </c>
+      <c r="H11" s="7">
+        <v>4</v>
+      </c>
       <c r="I11" s="7" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="J11" s="7">
         <v>10</v>
@@ -2497,20 +2494,22 @@
       <c r="L11" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="M11" s="7"/>
+      <c r="M11" s="7" t="s">
+        <v>25</v>
+      </c>
       <c r="O11" s="6" t="s">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="4">
-        <v>263046</v>
+        <v>263047</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" s="5">
         <v>8</v>
@@ -2519,20 +2518,18 @@
         <v>6</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="F12" s="8">
         <v>1</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="H12" s="7">
         <v>4</v>
       </c>
-      <c r="I12" s="7" t="s">
-        <v>25</v>
-      </c>
+      <c r="I12" s="7"/>
       <c r="J12" s="7">
         <v>10</v>
       </c>
@@ -2542,43 +2539,41 @@
       <c r="L12" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="7" t="s">
-        <v>26</v>
-      </c>
+      <c r="M12" s="7"/>
       <c r="O12" s="6" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" ht="17.399999999999999">
       <c r="A13" s="4">
-        <v>263047</v>
+        <v>263049</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>40</v>
       </c>
       <c r="C13" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F13" s="8">
-        <v>1</v>
-      </c>
+      <c r="F13" s="7"/>
       <c r="G13" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H13" s="7">
         <v>4</v>
       </c>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7">
+      <c r="I13" s="7">
+        <v>0.9</v>
+      </c>
+      <c r="J13" s="7" t="s">
         <v>10</v>
       </c>
       <c r="K13" s="8">
@@ -2587,62 +2582,53 @@
       <c r="L13" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="M13" s="7"/>
+      <c r="M13" s="7" t="s">
+        <v>3</v>
+      </c>
       <c r="O13" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="P13" s="6" t="s">
-        <v>139</v>
+        <v>40</v>
+      </c>
+      <c r="P13" s="17" t="s">
+        <v>134</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="17.399999999999999">
+    <row r="14" spans="1:16">
       <c r="A14" s="4">
-        <v>263049</v>
+        <v>263052</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>41</v>
       </c>
       <c r="C14" s="5">
-        <v>6</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>3</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H14" s="7">
+        <v>1.3</v>
+      </c>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7">
+        <v>5</v>
+      </c>
+      <c r="K14" s="8">
+        <v>1</v>
+      </c>
+      <c r="L14" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="7">
-        <v>0.9</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="K14" s="8">
-        <v>1</v>
-      </c>
-      <c r="L14" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="7" t="s">
-        <v>3</v>
-      </c>
+      <c r="M14" s="7"/>
       <c r="O14" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="P14" s="17" t="s">
-        <v>135</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="4">
-        <v>263052</v>
+        <v>263053</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>42</v>
@@ -2650,33 +2636,41 @@
       <c r="C15" s="5">
         <v>8</v>
       </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+      <c r="D15" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0.4</v>
+      </c>
       <c r="G15" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="7">
-        <v>1.3</v>
-      </c>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7">
+        <v>15</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7">
         <v>5</v>
       </c>
-      <c r="K15" s="8">
-        <v>1</v>
-      </c>
-      <c r="L15" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="M15" s="7"/>
       <c r="O15" s="6" t="s">
-        <v>105</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="4">
-        <v>263053</v>
+        <v>263056</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>43</v>
@@ -2685,43 +2679,44 @@
         <v>8</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="E16" s="7">
         <v>1</v>
       </c>
-      <c r="F16" s="8">
-        <v>0.4</v>
-      </c>
+      <c r="F16" s="7"/>
       <c r="G16" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J16" s="7">
         <v>10</v>
       </c>
-      <c r="I16" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7">
-        <v>5</v>
-      </c>
+      <c r="K16" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="M16" s="7"/>
       <c r="O16" s="6" t="s">
         <v>43</v>
+      </c>
+      <c r="P16" s="6" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:16">
       <c r="A17" s="4">
-        <v>263056</v>
+        <v>263059</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" s="5">
         <v>8</v>
@@ -2732,36 +2727,37 @@
       <c r="E17" s="7">
         <v>1</v>
       </c>
-      <c r="F17" s="7"/>
+      <c r="F17" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="G17" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>24</v>
+        <v>17</v>
+      </c>
+      <c r="H17" s="7">
+        <v>3</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="J17" s="7">
         <v>10</v>
       </c>
       <c r="K17" s="8">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>16</v>
+      </c>
       <c r="O17" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="P17" s="6" t="s">
-        <v>131</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:16">
       <c r="A18" s="4">
-        <v>263059</v>
+        <v>263079</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>46</v>
@@ -2770,22 +2766,22 @@
         <v>8</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E18" s="7">
         <v>1</v>
       </c>
-      <c r="F18" s="7" t="s">
-        <v>2</v>
+      <c r="F18" s="8">
+        <v>1</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H18" s="7">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J18" s="7">
         <v>10</v>
@@ -2794,18 +2790,18 @@
         <v>1</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="M18" s="7" t="s">
-        <v>16</v>
+        <v>3</v>
+      </c>
+      <c r="M18" s="7">
+        <v>3</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:16">
       <c r="A19" s="4">
-        <v>263079</v>
+        <v>263080</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>47</v>
@@ -2814,84 +2810,71 @@
         <v>8</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E19" s="7">
         <v>1</v>
       </c>
-      <c r="F19" s="8">
-        <v>1</v>
+      <c r="F19" s="7" t="s">
+        <v>2</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="I19" s="7">
+        <v>0.1</v>
       </c>
       <c r="J19" s="7">
-        <v>10</v>
-      </c>
-      <c r="K19" s="8">
-        <v>1</v>
+        <v>6.5</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>2</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="M19" s="7">
-        <v>3</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="M19" s="7"/>
       <c r="O19" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="4">
-        <v>263080</v>
+        <v>263082</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C20" s="5">
         <v>8</v>
       </c>
-      <c r="D20" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>2</v>
-      </c>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
       <c r="G20" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="J20" s="7">
-        <v>6.5</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>30</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H20" s="7">
+        <v>10</v>
+      </c>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
       <c r="M20" s="7"/>
       <c r="O20" s="6" t="s">
-        <v>101</v>
+        <v>119</v>
+      </c>
+      <c r="P20" s="6" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="4">
-        <v>263082</v>
+        <v>263084</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>50</v>
@@ -2899,30 +2882,39 @@
       <c r="C21" s="5">
         <v>8</v>
       </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
+      <c r="D21" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="7">
+        <v>2</v>
+      </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H21" s="7">
-        <v>10</v>
-      </c>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
+        <v>7</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21" s="7">
+        <v>15</v>
+      </c>
+      <c r="K21" s="8">
+        <v>1</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>3</v>
+      </c>
       <c r="M21" s="7"/>
       <c r="O21" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="P21" s="6" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:16">
       <c r="A22" s="4">
-        <v>263084</v>
+        <v>263090</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>51</v>
@@ -2931,38 +2923,40 @@
         <v>8</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E22" s="7">
+        <v>1</v>
+      </c>
+      <c r="F22" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F22" s="7"/>
       <c r="G22" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>49</v>
+        <v>6</v>
+      </c>
+      <c r="H22" s="7">
+        <v>1.2</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J22" s="7">
-        <v>15</v>
-      </c>
-      <c r="K22" s="8">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>2</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>3</v>
       </c>
       <c r="M22" s="7"/>
-      <c r="O22" s="6" t="s">
-        <v>106</v>
+      <c r="O22" s="10" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:16">
       <c r="A23" s="4">
-        <v>263090</v>
+        <v>263097</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>52</v>
@@ -2971,25 +2965,25 @@
         <v>8</v>
       </c>
       <c r="D23" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="7">
+        <v>10</v>
+      </c>
+      <c r="F23" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="G23" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E23" s="7">
-        <v>1</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>6</v>
-      </c>
       <c r="H23" s="7">
-        <v>1.2</v>
+        <v>8</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="J23" s="7">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>2</v>
@@ -2998,13 +2992,16 @@
         <v>3</v>
       </c>
       <c r="M23" s="7"/>
-      <c r="O23" s="10" t="s">
-        <v>97</v>
+      <c r="O23" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="P23" s="6" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:16">
       <c r="A24" s="4">
-        <v>263097</v>
+        <v>263099</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>53</v>
@@ -3013,43 +3010,45 @@
         <v>8</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E24" s="7">
+        <v>4</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="7">
+        <v>1</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J24" s="7">
         <v>10</v>
       </c>
-      <c r="F24" s="8">
-        <v>0.4</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H24" s="7">
-        <v>8</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="J24" s="7">
+      <c r="K24" s="8">
+        <v>1</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M24" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="K24" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="L24" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="7"/>
       <c r="O24" s="6" t="s">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:16">
       <c r="A25" s="4">
-        <v>263099</v>
+        <v>263100</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>54</v>
@@ -3057,46 +3056,27 @@
       <c r="C25" s="5">
         <v>8</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E25" s="7">
-        <v>4</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>15</v>
-      </c>
       <c r="H25" s="7">
-        <v>1</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="J25" s="7">
-        <v>10</v>
-      </c>
-      <c r="K25" s="8">
-        <v>1</v>
-      </c>
-      <c r="L25" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M25" s="7" t="s">
-        <v>21</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
       <c r="O25" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="P25" s="6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:16">
       <c r="A26" s="4">
-        <v>263100</v>
+        <v>263102</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>55</v>
@@ -3104,27 +3084,40 @@
       <c r="C26" s="5">
         <v>8</v>
       </c>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
+      <c r="D26" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1</v>
+      </c>
       <c r="F26" s="7"/>
       <c r="G26" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H26" s="7">
-        <v>90</v>
-      </c>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
+        <v>15</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="7">
+        <v>5</v>
+      </c>
+      <c r="K26" s="8">
+        <v>1</v>
+      </c>
       <c r="L26" s="7"/>
       <c r="M26" s="7"/>
       <c r="O26" s="6" t="s">
-        <v>110</v>
+        <v>55</v>
+      </c>
+      <c r="P26" s="6" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" ht="17.399999999999999">
       <c r="A27" s="4">
-        <v>263102</v>
+        <v>263103</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>56</v>
@@ -3133,39 +3126,43 @@
         <v>8</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E27" s="7">
         <v>1</v>
       </c>
-      <c r="F27" s="7"/>
+      <c r="F27" s="8">
+        <v>1</v>
+      </c>
       <c r="G27" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J27" s="7">
         <v>5</v>
       </c>
-      <c r="K27" s="8">
-        <v>1</v>
-      </c>
-      <c r="L27" s="7"/>
+      <c r="K27" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>16</v>
+      </c>
       <c r="M27" s="7"/>
       <c r="O27" s="6" t="s">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="17.399999999999999">
+    <row r="28" spans="1:16">
       <c r="A28" s="4">
-        <v>263103</v>
+        <v>263106</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>57</v>
@@ -3177,7 +3174,7 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F28" s="8">
         <v>1</v>
@@ -3185,101 +3182,103 @@
       <c r="G28" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H28" s="7" t="s">
-        <v>24</v>
+      <c r="H28" s="7">
+        <v>2</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J28" s="7">
-        <v>5</v>
-      </c>
-      <c r="K28" s="7" t="s">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="K28" s="8">
+        <v>1</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="M28" s="7"/>
       <c r="O28" s="6" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:16">
       <c r="A29" s="4">
-        <v>263106</v>
+        <v>263113</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C29" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E29" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F29" s="8">
         <v>1</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H29" s="7">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J29" s="7">
         <v>10</v>
       </c>
-      <c r="K29" s="8">
-        <v>1</v>
+      <c r="K29" s="7" t="s">
+        <v>2</v>
       </c>
       <c r="L29" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="M29" s="7"/>
-      <c r="O29" s="6" t="s">
-        <v>58</v>
+      <c r="M29" s="7">
+        <v>2.25</v>
+      </c>
+      <c r="O29" s="10" t="s">
+        <v>123</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:16">
       <c r="A30" s="4">
-        <v>263113</v>
+        <v>263125</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>59</v>
       </c>
       <c r="C30" s="5">
+        <v>8</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="E30" s="7">
+        <v>2</v>
+      </c>
+      <c r="F30" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="G30" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E30" s="7">
-        <v>1</v>
-      </c>
-      <c r="F30" s="8">
-        <v>1</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>7</v>
-      </c>
       <c r="H30" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>13</v>
+        <v>21</v>
+      </c>
+      <c r="I30" s="7">
+        <v>0.5</v>
       </c>
       <c r="J30" s="7">
         <v>10</v>
@@ -3293,16 +3292,13 @@
       <c r="M30" s="7">
         <v>2.25</v>
       </c>
-      <c r="O30" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="P30" s="6" t="s">
-        <v>108</v>
+      <c r="O30" s="6" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:16">
       <c r="A31" s="4">
-        <v>263125</v>
+        <v>263127</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>60</v>
@@ -3311,42 +3307,34 @@
         <v>8</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E31" s="7">
-        <v>2</v>
-      </c>
-      <c r="F31" s="8">
-        <v>0.8</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
       <c r="G31" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H31" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I31" s="7">
-        <v>0.5</v>
-      </c>
+      <c r="H31" s="7">
+        <v>2</v>
+      </c>
+      <c r="I31" s="7"/>
       <c r="J31" s="7">
         <v>10</v>
       </c>
-      <c r="K31" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="L31" s="7" t="s">
-        <v>3</v>
-      </c>
+      <c r="K31" s="8">
+        <v>1</v>
+      </c>
+      <c r="L31" s="7"/>
       <c r="M31" s="7">
-        <v>2.25</v>
+        <v>0.5</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" spans="1:16">
       <c r="A32" s="4">
-        <v>263127</v>
+        <v>263139</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>61</v>
@@ -3355,190 +3343,196 @@
         <v>8</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E32" s="7"/>
+        <v>12</v>
+      </c>
+      <c r="E32" s="7">
+        <v>1</v>
+      </c>
       <c r="F32" s="7"/>
       <c r="G32" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H32" s="7">
-        <v>2</v>
+      <c r="H32" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="I32" s="7"/>
       <c r="J32" s="7">
         <v>10</v>
       </c>
-      <c r="K32" s="8">
-        <v>1</v>
-      </c>
-      <c r="L32" s="7"/>
+      <c r="K32" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="L32" s="7" t="s">
+        <v>3</v>
+      </c>
       <c r="M32" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="O32" s="6" t="s">
-        <v>117</v>
+        <v>1</v>
+      </c>
+      <c r="O32" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="P32" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="33" spans="1:16">
       <c r="A33" s="4">
-        <v>263139</v>
+        <v>263153</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>62</v>
       </c>
       <c r="C33" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="E33" s="7">
-        <v>1</v>
-      </c>
-      <c r="F33" s="7"/>
+        <v>4</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="G33" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I33" s="7"/>
+        <v>14</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>18</v>
+      </c>
       <c r="J33" s="7">
-        <v>10</v>
-      </c>
-      <c r="K33" s="7" t="s">
         <v>2</v>
       </c>
+      <c r="K33" s="8">
+        <v>1.4</v>
+      </c>
       <c r="L33" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="M33" s="7">
-        <v>1</v>
-      </c>
-      <c r="O33" s="7" t="s">
-        <v>136</v>
+        <v>16</v>
+      </c>
+      <c r="M33" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="O33" s="6" t="s">
+        <v>122</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" spans="1:16">
       <c r="A34" s="4">
-        <v>263153</v>
+        <v>263155</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C34" s="5">
+        <v>8</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D34" s="7" t="s">
-        <v>64</v>
-      </c>
       <c r="E34" s="7">
-        <v>4</v>
-      </c>
-      <c r="F34" s="7" t="s">
         <v>2</v>
       </c>
+      <c r="F34" s="7"/>
       <c r="G34" s="7" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J34" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K34" s="8">
         <v>1.4</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="M34" s="7" t="s">
-        <v>26</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M34" s="7"/>
       <c r="O34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35" spans="1:16">
       <c r="A35" s="4">
-        <v>263155</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C35" s="5">
-        <v>8</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E35" s="7">
-        <v>2</v>
-      </c>
+        <v>263158</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" s="6">
+        <v>30</v>
+      </c>
+      <c r="E35" s="7"/>
       <c r="F35" s="7"/>
-      <c r="G35" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J35" s="7">
-        <v>5</v>
-      </c>
-      <c r="K35" s="8">
-        <v>1.4</v>
-      </c>
-      <c r="L35" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="7"/>
+      <c r="G35" s="6">
+        <v>100</v>
+      </c>
+      <c r="H35" s="6">
+        <v>1.35</v>
+      </c>
+      <c r="I35" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="J35" s="6">
+        <v>10</v>
+      </c>
+      <c r="K35" s="16">
+        <v>1</v>
+      </c>
+      <c r="L35" s="6">
+        <v>1</v>
+      </c>
+      <c r="M35" s="6"/>
       <c r="O35" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="P35" s="6" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:16">
       <c r="A36" s="4">
-        <v>263158</v>
+        <v>263159</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D36" s="6">
         <v>30</v>
       </c>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
+      <c r="E36" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>103</v>
+      </c>
       <c r="G36" s="6">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H36" s="6">
-        <v>1.35</v>
+        <v>3</v>
       </c>
       <c r="I36" s="6">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="J36" s="6">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K36" s="16">
         <v>1</v>
@@ -3550,55 +3544,13 @@
       <c r="O36" s="6" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="37" spans="1:16">
-      <c r="A37" s="4">
-        <v>263159</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C37" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="D37" s="6">
-        <v>30</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="G37" s="6">
-        <v>80</v>
-      </c>
-      <c r="H37" s="6">
-        <v>3</v>
-      </c>
-      <c r="I37" s="6">
-        <v>0.02</v>
-      </c>
-      <c r="J37" s="6">
-        <v>20</v>
-      </c>
-      <c r="K37" s="16">
-        <v>1</v>
-      </c>
-      <c r="L37" s="6">
-        <v>1</v>
-      </c>
-      <c r="M37" s="6"/>
-      <c r="O37" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="P37" s="11"/>
+      <c r="P36" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O30 O23 O4 O6" xr:uid="{500EDB87-BE25-4BF9-A964-6A9D4ABEB59F}">
-      <formula1>$O$4:$O$37</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O29 O4 O22" xr:uid="{500EDB87-BE25-4BF9-A964-6A9D4ABEB59F}">
+      <formula1>$O$4:$O$36</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/JsonConverter/ExcelFiles/Weapon.xlsx
+++ b/JsonConverter/ExcelFiles/Weapon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\Project\Vamsurlike\Vamsurlike\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC535F4-1088-41D2-9616-D7B61A577D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89924097-E860-411D-B397-DFF3E498AA5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-31680" yWindow="336" windowWidth="28284" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WeaponStats" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="138">
   <si>
     <t>108Bocce</t>
   </si>
@@ -28,9 +28,6 @@
     <t>10</t>
   </si>
   <si>
-    <t>100%</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
@@ -118,9 +115,6 @@
     <t>0.025</t>
   </si>
   <si>
-    <t>80%</t>
-  </si>
-  <si>
     <t>EightTheSparrow</t>
   </si>
   <si>
@@ -160,9 +154,6 @@
     <t>GreatestJubilee</t>
   </si>
   <si>
-    <t>KingBible</t>
-  </si>
-  <si>
     <t>Knife</t>
   </si>
   <si>
@@ -330,12 +321,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>PatternType</t>
-  </si>
-  <si>
-    <t>WeaponPatternType</t>
-  </si>
-  <si>
     <t>Projectile</t>
   </si>
   <si>
@@ -359,10 +344,6 @@
   </si>
   <si>
     <t>FireWand</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>75%</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -965,6 +946,21 @@
   <si>
     <t>무지개빛 미사일이 현란하게 쏟아지며 캐릭터 주위 좁은 원형 범위를 폭격,  쏟아지는 속도는 투사체 속도의 형향 받음</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KingBible</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PatternType</t>
   </si>
 </sst>
 </file>
@@ -1131,7 +1127,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1150,9 +1146,6 @@
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1164,10 +1157,23 @@
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1185,6 +1191,37 @@
         <vertAlign val="baseline"/>
         <color theme="1"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color theme="1"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="0" tint="-0.249977111117893"/>
@@ -1533,37 +1570,7 @@
         <vertAlign val="baseline"/>
         <color theme="1"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1571,7 +1578,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color auto="1"/>
         </left>
@@ -1854,12 +1861,12 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="CoolTIme" dataDxfId="11"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="RepeatInterval" dataDxfId="10"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="BaseDamage" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Range" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Knockback" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Duration" dataDxfId="6"/>
-    <tableColumn id="15" xr3:uid="{63E72993-8C0A-4AC4-8D91-D518A58C0491}" name="Evolution" dataDxfId="5" totalsRowDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{A9A8A944-4E2C-4752-B501-2B33ACD25188}" name="PatternType" dataDxfId="3" totalsRowDxfId="2"/>
-    <tableColumn id="16" xr3:uid="{2137CC88-8B38-4E75-A6B3-68DE8E1FFBCF}" name="열1" dataDxfId="1" totalsRowDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Range" dataDxfId="0"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Knockback" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Duration" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{63E72993-8C0A-4AC4-8D91-D518A58C0491}" name="Evolution" dataDxfId="6" totalsRowDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{A9A8A944-4E2C-4752-B501-2B33ACD25188}" name="PatternType" dataDxfId="4" totalsRowDxfId="3"/>
+    <tableColumn id="16" xr3:uid="{2137CC88-8B38-4E75-A6B3-68DE8E1FFBCF}" name="열1" dataDxfId="2" totalsRowDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2020,8 +2027,9 @@
     <col min="1" max="1" width="11.5" style="2" customWidth="1"/>
     <col min="2" max="2" width="14" style="6" customWidth="1"/>
     <col min="3" max="3" width="12.296875" style="5" customWidth="1"/>
-    <col min="4" max="11" width="14" style="6" customWidth="1"/>
-    <col min="12" max="13" width="8.796875" style="14"/>
+    <col min="4" max="10" width="14" style="6" customWidth="1"/>
+    <col min="11" max="11" width="14" style="19" customWidth="1"/>
+    <col min="12" max="13" width="8.796875" style="13"/>
     <col min="14" max="15" width="14" style="6" customWidth="1"/>
     <col min="16" max="16384" width="8.796875" style="6"/>
   </cols>
@@ -2030,124 +2038,124 @@
       <c r="A1" s="1"/>
       <c r="C1" s="2"/>
       <c r="D1" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E1" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I1" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>85</v>
+      <c r="K1" s="19" t="s">
+        <v>82</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>67</v>
+        <v>136</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>67</v>
+        <v>136</v>
+      </c>
+      <c r="K2" s="20" t="s">
+        <v>136</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="17.55" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I3" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="J3" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="K3" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="M3" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="N3" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="O3" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="P3" s="12" t="s">
-        <v>108</v>
+      <c r="N3" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="P3" s="11" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2162,78 +2170,78 @@
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="7" t="s">
         <v>2</v>
       </c>
+      <c r="F4" s="18">
+        <v>1</v>
+      </c>
       <c r="G4" s="7" t="s">
         <v>1</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I4" s="7"/>
       <c r="J4" s="7">
         <v>12</v>
       </c>
-      <c r="K4" s="7" t="s">
-        <v>2</v>
+      <c r="K4" s="22">
+        <v>1</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M4" s="7"/>
-      <c r="N4" s="10"/>
+      <c r="N4" s="9"/>
       <c r="O4" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="P4" s="10"/>
+        <v>92</v>
+      </c>
+      <c r="P4" s="9"/>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="4">
         <v>263003</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C5" s="5">
         <v>8</v>
       </c>
       <c r="D5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="7">
+        <v>1</v>
+      </c>
+      <c r="F5" s="18"/>
+      <c r="G5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="7">
-        <v>1</v>
-      </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="I5" s="7" t="s">
         <v>8</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>9</v>
       </c>
       <c r="J5" s="7">
         <v>10</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="22">
         <v>1</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M5" s="7"/>
-      <c r="N5" s="18">
+      <c r="N5" s="16">
         <v>264061</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2241,47 +2249,47 @@
         <v>263020</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" s="5">
         <v>7</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" s="7">
         <v>1</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>2</v>
+      <c r="F6" s="18">
+        <v>1</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J6" s="7">
         <v>10</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="K6" s="22">
+        <v>1</v>
+      </c>
+      <c r="L6" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="L6" s="7" t="s">
-        <v>3</v>
-      </c>
       <c r="M6" s="7"/>
-      <c r="N6" s="18">
+      <c r="N6" s="16">
         <v>264027</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2289,37 +2297,37 @@
         <v>263023</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" s="5">
         <v>8</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
+      <c r="F7" s="18"/>
       <c r="G7" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
+      <c r="K7" s="22"/>
       <c r="L7" s="7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M7" s="7">
         <v>2</v>
       </c>
-      <c r="N7" s="18">
+      <c r="N7" s="16">
         <v>264016</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2327,46 +2335,46 @@
         <v>263036</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" s="5">
         <v>8</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8" s="7">
         <v>4</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>32</v>
+      <c r="F8" s="18">
+        <v>0.8</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J8" s="7">
         <v>10</v>
       </c>
-      <c r="K8" s="8">
+      <c r="K8" s="22">
         <v>1</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="17.399999999999999">
@@ -2374,44 +2382,44 @@
         <v>263037</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C9" s="5">
         <v>8</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" s="7">
         <v>1</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="18">
         <v>1</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J9" s="7">
         <v>5</v>
       </c>
-      <c r="K9" s="7" t="s">
-        <v>2</v>
+      <c r="K9" s="22">
+        <v>1</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M9" s="7"/>
       <c r="O9" s="6" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2419,42 +2427,42 @@
         <v>263041</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C10" s="5">
         <v>1</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E10" s="7">
         <v>1</v>
       </c>
-      <c r="F10" s="7"/>
+      <c r="F10" s="18"/>
       <c r="G10" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J10" s="7">
         <v>10</v>
       </c>
-      <c r="K10" s="8">
+      <c r="K10" s="22">
         <v>1</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M10" s="7"/>
       <c r="O10" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2462,46 +2470,46 @@
         <v>263046</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C11" s="5">
         <v>8</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="8">
+        <v>36</v>
+      </c>
+      <c r="F11" s="18">
         <v>1</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H11" s="7">
         <v>4</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J11" s="7">
         <v>10</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K11" s="22">
         <v>1</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2509,22 +2517,22 @@
         <v>263047</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C12" s="5">
         <v>8</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="8">
+        <v>2</v>
+      </c>
+      <c r="F12" s="18">
         <v>1</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H12" s="7">
         <v>4</v>
@@ -2533,18 +2541,18 @@
       <c r="J12" s="7">
         <v>10</v>
       </c>
-      <c r="K12" s="8">
+      <c r="K12" s="22">
         <v>1</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M12" s="7"/>
       <c r="O12" s="6" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="17.399999999999999">
@@ -2552,20 +2560,20 @@
         <v>263049</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C13" s="5">
         <v>6</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F13" s="7"/>
+        <v>2</v>
+      </c>
+      <c r="F13" s="18"/>
       <c r="G13" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H13" s="7">
         <v>4</v>
@@ -2574,22 +2582,22 @@
         <v>0.9</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="K13" s="8">
+        <v>9</v>
+      </c>
+      <c r="K13" s="22">
         <v>1</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="P13" s="17" t="s">
-        <v>134</v>
+        <v>38</v>
+      </c>
+      <c r="P13" s="15" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2597,16 +2605,16 @@
         <v>263052</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C14" s="5">
         <v>8</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
+      <c r="F14" s="18"/>
       <c r="G14" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H14" s="7">
         <v>1.3</v>
@@ -2615,15 +2623,15 @@
       <c r="J14" s="7">
         <v>5</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="22">
         <v>1</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M14" s="7"/>
       <c r="O14" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2631,41 +2639,41 @@
         <v>263053</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C15" s="5">
         <v>8</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E15" s="7">
         <v>1</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="18">
         <v>0.4</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J15" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="K15" s="7" t="s">
-        <v>2</v>
+      <c r="K15" s="22">
+        <v>1</v>
       </c>
       <c r="L15" s="7"/>
       <c r="M15" s="7">
         <v>5</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2673,42 +2681,42 @@
         <v>263056</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C16" s="5">
         <v>8</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E16" s="7">
         <v>1</v>
       </c>
-      <c r="F16" s="7"/>
+      <c r="F16" s="18"/>
       <c r="G16" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J16" s="7">
         <v>10</v>
       </c>
-      <c r="K16" s="8">
+      <c r="K16" s="22">
         <v>0.7</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M16" s="7"/>
       <c r="O16" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2716,43 +2724,43 @@
         <v>263059</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C17" s="5">
         <v>8</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17" s="7">
         <v>1</v>
       </c>
-      <c r="F17" s="7" t="s">
-        <v>2</v>
+      <c r="F17" s="18">
+        <v>1</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H17" s="7">
         <v>3</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J17" s="7">
         <v>10</v>
       </c>
-      <c r="K17" s="8">
+      <c r="K17" s="22">
         <v>1</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2760,43 +2768,43 @@
         <v>263079</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>46</v>
+        <v>134</v>
       </c>
       <c r="C18" s="5">
         <v>8</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E18" s="7">
         <v>1</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="18">
         <v>1</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>4</v>
+        <v>135</v>
       </c>
       <c r="J18" s="7">
         <v>10</v>
       </c>
-      <c r="K18" s="8">
+      <c r="K18" s="22">
         <v>1</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M18" s="7">
         <v>3</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2804,25 +2812,25 @@
         <v>263080</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C19" s="5">
         <v>8</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E19" s="7">
         <v>1</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="18">
+        <v>1</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H19" s="7" t="s">
         <v>2</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>3</v>
       </c>
       <c r="I19" s="7">
         <v>0.1</v>
@@ -2830,15 +2838,15 @@
       <c r="J19" s="7">
         <v>6.5</v>
       </c>
-      <c r="K19" s="7" t="s">
-        <v>2</v>
+      <c r="K19" s="22">
+        <v>1</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M19" s="7"/>
       <c r="O19" s="6" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2846,30 +2854,30 @@
         <v>263082</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C20" s="5">
         <v>8</v>
       </c>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
+      <c r="F20" s="18"/>
       <c r="G20" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H20" s="7">
         <v>10</v>
       </c>
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
+      <c r="K20" s="22"/>
       <c r="L20" s="7"/>
       <c r="M20" s="7"/>
       <c r="O20" s="6" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2877,39 +2885,39 @@
         <v>263084</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C21" s="5">
         <v>8</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E21" s="7">
         <v>2</v>
       </c>
-      <c r="F21" s="7"/>
+      <c r="F21" s="18"/>
       <c r="G21" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J21" s="7">
         <v>15</v>
       </c>
-      <c r="K21" s="8">
+      <c r="K21" s="22">
         <v>1</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M21" s="7"/>
       <c r="O21" s="6" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2917,41 +2925,41 @@
         <v>263090</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C22" s="5">
         <v>8</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E22" s="7">
         <v>1</v>
       </c>
-      <c r="F22" s="7" t="s">
-        <v>2</v>
+      <c r="F22" s="18">
+        <v>1</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H22" s="7">
         <v>1.2</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J22" s="7">
         <v>10</v>
       </c>
-      <c r="K22" s="7" t="s">
+      <c r="K22" s="22">
+        <v>1</v>
+      </c>
+      <c r="L22" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="L22" s="7" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="7"/>
-      <c r="O22" s="10" t="s">
-        <v>96</v>
+      <c r="O22" s="9" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2959,44 +2967,44 @@
         <v>263097</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C23" s="5">
         <v>8</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E23" s="7">
         <v>10</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="18">
         <v>0.4</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H23" s="7">
         <v>8</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J23" s="7">
         <v>20</v>
       </c>
-      <c r="K23" s="7" t="s">
+      <c r="K23" s="22">
+        <v>1</v>
+      </c>
+      <c r="L23" s="7" t="s">
         <v>2</v>
-      </c>
-      <c r="L23" s="7" t="s">
-        <v>3</v>
       </c>
       <c r="M23" s="7"/>
       <c r="O23" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="P23" s="6" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3004,46 +3012,46 @@
         <v>263099</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C24" s="5">
         <v>8</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E24" s="7">
         <v>4</v>
       </c>
-      <c r="F24" s="7" t="s">
-        <v>32</v>
+      <c r="F24" s="18">
+        <v>0.8</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H24" s="7">
         <v>1</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J24" s="7">
         <v>10</v>
       </c>
-      <c r="K24" s="8">
+      <c r="K24" s="22">
         <v>1</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3051,27 +3059,27 @@
         <v>263100</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C25" s="5">
         <v>8</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
+      <c r="F25" s="18"/>
       <c r="G25" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H25" s="7">
         <v>90</v>
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
+      <c r="K25" s="22"/>
       <c r="L25" s="7"/>
       <c r="M25" s="7"/>
       <c r="O25" s="6" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3079,40 +3087,40 @@
         <v>263102</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C26" s="5">
         <v>8</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E26" s="7">
         <v>1</v>
       </c>
-      <c r="F26" s="7"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I26" s="7" t="s">
         <v>15</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>16</v>
       </c>
       <c r="J26" s="7">
         <v>5</v>
       </c>
-      <c r="K26" s="8">
+      <c r="K26" s="22">
         <v>1</v>
       </c>
       <c r="L26" s="7"/>
       <c r="M26" s="7"/>
       <c r="O26" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="17.399999999999999">
@@ -3120,44 +3128,44 @@
         <v>263103</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C27" s="5">
         <v>8</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E27" s="7">
         <v>1</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="18">
         <v>1</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J27" s="7">
         <v>5</v>
       </c>
-      <c r="K27" s="7" t="s">
-        <v>2</v>
+      <c r="K27" s="22">
+        <v>1</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M27" s="7"/>
       <c r="O27" s="6" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3165,44 +3173,44 @@
         <v>263106</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C28" s="5">
         <v>8</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E28" s="7">
         <v>4</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="18">
         <v>1</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H28" s="7">
         <v>2</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J28" s="7">
         <v>10</v>
       </c>
-      <c r="K28" s="8">
+      <c r="K28" s="22">
         <v>1</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M28" s="7"/>
       <c r="O28" s="6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3210,46 +3218,46 @@
         <v>263113</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C29" s="5">
         <v>6</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E29" s="7">
         <v>1</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="18">
         <v>1</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J29" s="7">
         <v>10</v>
       </c>
-      <c r="K29" s="7" t="s">
+      <c r="K29" s="22">
+        <v>1</v>
+      </c>
+      <c r="L29" s="7" t="s">
         <v>2</v>
-      </c>
-      <c r="L29" s="7" t="s">
-        <v>3</v>
       </c>
       <c r="M29" s="7">
         <v>2.25</v>
       </c>
-      <c r="O29" s="10" t="s">
-        <v>123</v>
+      <c r="O29" s="9" t="s">
+        <v>117</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3257,25 +3265,25 @@
         <v>263125</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C30" s="5">
         <v>8</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30" s="7">
         <v>2</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="18">
         <v>0.8</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I30" s="7">
         <v>0.5</v>
@@ -3283,17 +3291,17 @@
       <c r="J30" s="7">
         <v>10</v>
       </c>
-      <c r="K30" s="7" t="s">
+      <c r="K30" s="22">
+        <v>1</v>
+      </c>
+      <c r="L30" s="7" t="s">
         <v>2</v>
-      </c>
-      <c r="L30" s="7" t="s">
-        <v>3</v>
       </c>
       <c r="M30" s="7">
         <v>2.25</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3301,18 +3309,18 @@
         <v>263127</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C31" s="5">
         <v>8</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
+      <c r="F31" s="18"/>
       <c r="G31" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H31" s="7">
         <v>2</v>
@@ -3321,7 +3329,7 @@
       <c r="J31" s="7">
         <v>10</v>
       </c>
-      <c r="K31" s="8">
+      <c r="K31" s="22">
         <v>1</v>
       </c>
       <c r="L31" s="7"/>
@@ -3329,7 +3337,7 @@
         <v>0.5</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3337,42 +3345,42 @@
         <v>263139</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C32" s="5">
         <v>8</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E32" s="7">
         <v>1</v>
       </c>
-      <c r="F32" s="7"/>
+      <c r="F32" s="18"/>
       <c r="G32" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I32" s="7"/>
       <c r="J32" s="7">
         <v>10</v>
       </c>
-      <c r="K32" s="7" t="s">
+      <c r="K32" s="22">
+        <v>1</v>
+      </c>
+      <c r="L32" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="L32" s="7" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="7">
         <v>1</v>
       </c>
       <c r="O32" s="7" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3380,46 +3388,46 @@
         <v>263153</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C33" s="5">
         <v>6</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E33" s="7">
         <v>4</v>
       </c>
-      <c r="F33" s="7" t="s">
-        <v>2</v>
+      <c r="F33" s="18">
+        <v>1</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J33" s="7">
         <v>2</v>
       </c>
-      <c r="K33" s="8">
+      <c r="K33" s="22">
         <v>1.4</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M33" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3427,42 +3435,42 @@
         <v>263155</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C34" s="5">
         <v>8</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E34" s="7">
         <v>2</v>
       </c>
-      <c r="F34" s="7"/>
+      <c r="F34" s="18"/>
       <c r="G34" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J34" s="7">
         <v>5</v>
       </c>
-      <c r="K34" s="8">
+      <c r="K34" s="22">
         <v>1.4</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M34" s="7"/>
       <c r="O34" s="6" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3470,16 +3478,16 @@
         <v>263158</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>72</v>
+        <v>93</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>69</v>
       </c>
       <c r="D35" s="6">
         <v>30</v>
       </c>
       <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
+      <c r="F35" s="18"/>
       <c r="G35" s="6">
         <v>100</v>
       </c>
@@ -3492,7 +3500,7 @@
       <c r="J35" s="6">
         <v>10</v>
       </c>
-      <c r="K35" s="16">
+      <c r="K35" s="19">
         <v>1</v>
       </c>
       <c r="L35" s="6">
@@ -3500,7 +3508,7 @@
       </c>
       <c r="M35" s="6"/>
       <c r="O35" s="6" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3508,19 +3516,19 @@
         <v>263159</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>72</v>
+        <v>97</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>69</v>
       </c>
       <c r="D36" s="6">
         <v>30</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>103</v>
+        <v>68</v>
+      </c>
+      <c r="F36" s="18">
+        <v>0.75</v>
       </c>
       <c r="G36" s="6">
         <v>80</v>
@@ -3534,7 +3542,7 @@
       <c r="J36" s="6">
         <v>20</v>
       </c>
-      <c r="K36" s="16">
+      <c r="K36" s="19">
         <v>1</v>
       </c>
       <c r="L36" s="6">
@@ -3542,9 +3550,9 @@
       </c>
       <c r="M36" s="6"/>
       <c r="O36" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="P36" s="11"/>
+        <v>95</v>
+      </c>
+      <c r="P36" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/JsonConverter/ExcelFiles/Weapon.xlsx
+++ b/JsonConverter/ExcelFiles/Weapon.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\Project\Vamsurlike\Vamsurlike\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8ACB77-7C2A-490A-9AD5-B50C05B89748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2976F58-A1C5-4DC0-9263-34BB625E1A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="816" windowWidth="28284" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28152" yWindow="1092" windowWidth="28080" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WeaponStats" sheetId="1" r:id="rId1"/>
@@ -3541,7 +3541,7 @@
         <v>10</v>
       </c>
       <c r="K36" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" s="6">
         <v>1</v>

--- a/JsonConverter/ExcelFiles/Weapon.xlsx
+++ b/JsonConverter/ExcelFiles/Weapon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\Project\Vamsurlike\Vamsurlike\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6389B1C-6066-4544-8B3E-C4EE0B98F246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9498964A-C7B4-46F1-9202-B0A01450C47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="552" yWindow="1932" windowWidth="28080" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-29088" yWindow="792" windowWidth="28080" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WeaponStats" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="71">
   <si>
     <t>1</t>
   </si>
@@ -258,6 +258,22 @@
   </si>
   <si>
     <t>1.3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>60</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1430,7 +1446,7 @@
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="11.5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.796875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="19.796875" style="6" customWidth="1"/>
     <col min="3" max="3" width="8.69921875" style="5" customWidth="1"/>
     <col min="4" max="4" width="7.796875" style="6" customWidth="1"/>
     <col min="5" max="5" width="8.796875" style="6" customWidth="1"/>
@@ -1442,7 +1458,10 @@
     <col min="12" max="13" width="8.796875" style="12"/>
     <col min="14" max="14" width="7" style="6" customWidth="1"/>
     <col min="15" max="15" width="14" style="6" customWidth="1"/>
-    <col min="16" max="16384" width="8.796875" style="6"/>
+    <col min="16" max="16" width="18.19921875" style="6" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.8984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.796875" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="17.399999999999999">
@@ -1595,7 +1614,7 @@
       <c r="E4" s="16"/>
       <c r="F4" s="16"/>
       <c r="G4" s="16" t="s">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="H4" s="16" t="s">
         <v>65</v>
@@ -1662,9 +1681,14 @@
       </c>
       <c r="N5" s="14"/>
       <c r="O5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q5" s="14"/>
+        <v>52</v>
+      </c>
+      <c r="P5" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="14" t="s">
+        <v>67</v>
+      </c>
       <c r="R5" s="14"/>
     </row>
     <row r="6" spans="1:18">
@@ -1784,7 +1808,7 @@
       </c>
       <c r="F8" s="16"/>
       <c r="G8" s="16" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="H8" s="16" t="s">
         <v>18</v>
@@ -1806,7 +1830,12 @@
       <c r="O8" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="Q8" s="14"/>
+      <c r="P8" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="14" t="s">
+        <v>68</v>
+      </c>
       <c r="R8" s="14"/>
     </row>
     <row r="9" spans="1:18">
@@ -1870,7 +1899,7 @@
         <v>26</v>
       </c>
       <c r="G10" s="14">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H10" s="14">
         <v>3</v>
